--- a/java/verify/fixtures/大表压精度（ods_t_big）.xlsx
+++ b/java/verify/fixtures/大表压精度（ods_t_big）.xlsx
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C2" t="n">
         <v>12345678901234.12</v>
@@ -469,7 +469,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C3" t="n">
         <v>12345678901234.12</v>
@@ -490,7 +490,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C4" t="n">
         <v>12345678901234.12</v>
@@ -511,7 +511,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C5" t="n">
         <v>12345678901234.12</v>
@@ -532,7 +532,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C6" t="n">
         <v>12345678901234.12</v>
@@ -553,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C7" t="n">
         <v>12345678901234.12</v>
@@ -574,7 +574,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C8" t="n">
         <v>12345678901234.12</v>
@@ -595,7 +595,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C9" t="n">
         <v>12345678901234.12</v>
@@ -616,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C10" t="n">
         <v>12345678901234.12</v>
@@ -637,7 +637,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C11" t="n">
         <v>12345678901234.12</v>
@@ -658,7 +658,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C12" t="n">
         <v>12345678901234.12</v>
@@ -679,7 +679,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C13" t="n">
         <v>12345678901234.12</v>
@@ -700,7 +700,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C14" t="n">
         <v>12345678901234.12</v>
@@ -721,7 +721,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C15" t="n">
         <v>12345678901234.12</v>
@@ -742,7 +742,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C16" t="n">
         <v>12345678901234.12</v>
@@ -763,7 +763,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C17" t="n">
         <v>12345678901234.12</v>
@@ -784,7 +784,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C18" t="n">
         <v>12345678901234.12</v>
@@ -805,7 +805,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C19" t="n">
         <v>12345678901234.12</v>
@@ -826,7 +826,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C20" t="n">
         <v>12345678901234.12</v>
@@ -847,7 +847,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C21" t="n">
         <v>12345678901234.12</v>
@@ -868,7 +868,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C22" t="n">
         <v>12345678901234.12</v>
@@ -889,7 +889,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C23" t="n">
         <v>12345678901234.12</v>
@@ -910,7 +910,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C24" t="n">
         <v>12345678901234.12</v>
@@ -931,7 +931,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C25" t="n">
         <v>12345678901234.12</v>
@@ -952,7 +952,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C26" t="n">
         <v>12345678901234.12</v>
@@ -973,7 +973,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C27" t="n">
         <v>12345678901234.12</v>
@@ -994,7 +994,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C28" t="n">
         <v>12345678901234.12</v>
@@ -1015,7 +1015,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C29" t="n">
         <v>12345678901234.12</v>
@@ -1036,7 +1036,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C30" t="n">
         <v>12345678901234.12</v>
@@ -1057,7 +1057,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C31" t="n">
         <v>12345678901234.12</v>
@@ -1078,7 +1078,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C32" t="n">
         <v>12345678901234.12</v>
@@ -1099,7 +1099,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C33" t="n">
         <v>12345678901234.12</v>
@@ -1120,7 +1120,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C34" t="n">
         <v>12345678901234.12</v>
@@ -1141,7 +1141,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C35" t="n">
         <v>12345678901234.12</v>
@@ -1162,7 +1162,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C36" t="n">
         <v>12345678901234.12</v>
@@ -1183,7 +1183,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C37" t="n">
         <v>12345678901234.12</v>
@@ -1204,7 +1204,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C38" t="n">
         <v>12345678901234.12</v>
@@ -1225,7 +1225,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C39" t="n">
         <v>12345678901234.12</v>
@@ -1246,7 +1246,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C40" t="n">
         <v>12345678901234.12</v>
@@ -1267,7 +1267,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C41" t="n">
         <v>12345678901234.12</v>
@@ -1288,7 +1288,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C42" t="n">
         <v>12345678901234.12</v>
@@ -1309,7 +1309,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C43" t="n">
         <v>12345678901234.12</v>
@@ -1330,7 +1330,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C44" t="n">
         <v>12345678901234.12</v>
@@ -1351,7 +1351,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C45" t="n">
         <v>12345678901234.12</v>
@@ -1372,7 +1372,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C46" t="n">
         <v>12345678901234.12</v>
@@ -1393,7 +1393,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C47" t="n">
         <v>12345678901234.12</v>
@@ -1414,7 +1414,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C48" t="n">
         <v>12345678901234.12</v>
@@ -1435,7 +1435,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C49" t="n">
         <v>12345678901234.12</v>
@@ -1456,7 +1456,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C50" t="n">
         <v>12345678901234.12</v>
@@ -1477,7 +1477,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C51" t="n">
         <v>12345678901234.12</v>
@@ -1498,7 +1498,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C52" t="n">
         <v>12345678901234.12</v>
@@ -1519,7 +1519,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C53" t="n">
         <v>12345678901234.12</v>
@@ -1540,7 +1540,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C54" t="n">
         <v>12345678901234.12</v>
@@ -1561,7 +1561,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C55" t="n">
         <v>12345678901234.12</v>
@@ -1582,7 +1582,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C56" t="n">
         <v>12345678901234.12</v>
@@ -1603,7 +1603,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C57" t="n">
         <v>12345678901234.12</v>
@@ -1624,7 +1624,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C58" t="n">
         <v>12345678901234.12</v>
@@ -1645,7 +1645,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C59" t="n">
         <v>12345678901234.12</v>
@@ -1666,7 +1666,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C60" t="n">
         <v>12345678901234.12</v>
@@ -1687,7 +1687,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C61" t="n">
         <v>12345678901234.12</v>
@@ -1708,7 +1708,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C62" t="n">
         <v>12345678901234.12</v>
@@ -1729,7 +1729,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C63" t="n">
         <v>12345678901234.12</v>
@@ -1750,7 +1750,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C64" t="n">
         <v>12345678901234.12</v>
@@ -1771,7 +1771,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C65" t="n">
         <v>12345678901234.12</v>
@@ -1792,7 +1792,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C66" t="n">
         <v>12345678901234.12</v>
@@ -1813,7 +1813,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C67" t="n">
         <v>12345678901234.12</v>
@@ -1834,7 +1834,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C68" t="n">
         <v>12345678901234.12</v>
@@ -1855,7 +1855,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C69" t="n">
         <v>12345678901234.12</v>
@@ -1876,7 +1876,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C70" t="n">
         <v>12345678901234.12</v>
@@ -1897,7 +1897,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C71" t="n">
         <v>12345678901234.12</v>
@@ -1918,7 +1918,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C72" t="n">
         <v>12345678901234.12</v>
@@ -1939,7 +1939,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C73" t="n">
         <v>12345678901234.12</v>
@@ -1960,7 +1960,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C74" t="n">
         <v>12345678901234.12</v>
@@ -1981,7 +1981,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C75" t="n">
         <v>12345678901234.12</v>
@@ -2002,7 +2002,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C76" t="n">
         <v>12345678901234.12</v>
@@ -2023,7 +2023,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C77" t="n">
         <v>12345678901234.12</v>
@@ -2044,7 +2044,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C78" t="n">
         <v>12345678901234.12</v>
@@ -2065,7 +2065,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C79" t="n">
         <v>12345678901234.12</v>
@@ -2086,7 +2086,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C80" t="n">
         <v>12345678901234.12</v>
@@ -2107,7 +2107,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C81" t="n">
         <v>12345678901234.12</v>
@@ -2128,7 +2128,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C82" t="n">
         <v>12345678901234.12</v>
@@ -2149,7 +2149,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C83" t="n">
         <v>12345678901234.12</v>
@@ -2170,7 +2170,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C84" t="n">
         <v>12345678901234.12</v>
@@ -2191,7 +2191,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C85" t="n">
         <v>12345678901234.12</v>
@@ -2212,7 +2212,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C86" t="n">
         <v>12345678901234.12</v>
@@ -2233,7 +2233,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C87" t="n">
         <v>12345678901234.12</v>
@@ -2254,7 +2254,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C88" t="n">
         <v>12345678901234.12</v>
@@ -2275,7 +2275,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C89" t="n">
         <v>12345678901234.12</v>
@@ -2296,7 +2296,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C90" t="n">
         <v>12345678901234.12</v>
@@ -2317,7 +2317,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C91" t="n">
         <v>12345678901234.12</v>
@@ -2338,7 +2338,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C92" t="n">
         <v>12345678901234.12</v>
@@ -2359,7 +2359,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C93" t="n">
         <v>12345678901234.12</v>
@@ -2380,7 +2380,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C94" t="n">
         <v>12345678901234.12</v>
@@ -2401,7 +2401,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C95" t="n">
         <v>12345678901234.12</v>
@@ -2422,7 +2422,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C96" t="n">
         <v>12345678901234.12</v>
@@ -2443,7 +2443,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C97" t="n">
         <v>12345678901234.12</v>
@@ -2464,7 +2464,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C98" t="n">
         <v>12345678901234.12</v>
@@ -2485,7 +2485,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C99" t="n">
         <v>12345678901234.12</v>
@@ -2506,7 +2506,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C100" t="n">
         <v>12345678901234.12</v>
@@ -2527,7 +2527,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C101" t="n">
         <v>12345678901234.12</v>
@@ -2548,7 +2548,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C102" t="n">
         <v>12345678901234.12</v>
@@ -2569,7 +2569,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C103" t="n">
         <v>12345678901234.12</v>
@@ -2590,7 +2590,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C104" t="n">
         <v>12345678901234.12</v>
@@ -2611,7 +2611,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C105" t="n">
         <v>12345678901234.12</v>
@@ -2632,7 +2632,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C106" t="n">
         <v>12345678901234.12</v>
@@ -2653,7 +2653,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C107" t="n">
         <v>12345678901234.12</v>
@@ -2674,7 +2674,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C108" t="n">
         <v>12345678901234.12</v>
@@ -2695,7 +2695,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C109" t="n">
         <v>12345678901234.12</v>
@@ -2716,7 +2716,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C110" t="n">
         <v>12345678901234.12</v>
@@ -2737,7 +2737,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C111" t="n">
         <v>12345678901234.12</v>
@@ -2758,7 +2758,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C112" t="n">
         <v>12345678901234.12</v>
@@ -2779,7 +2779,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C113" t="n">
         <v>12345678901234.12</v>
@@ -2800,7 +2800,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C114" t="n">
         <v>12345678901234.12</v>
@@ -2821,7 +2821,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C115" t="n">
         <v>12345678901234.12</v>
@@ -2842,7 +2842,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C116" t="n">
         <v>12345678901234.12</v>
@@ -2863,7 +2863,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C117" t="n">
         <v>12345678901234.12</v>
@@ -2884,7 +2884,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C118" t="n">
         <v>12345678901234.12</v>
@@ -2905,7 +2905,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C119" t="n">
         <v>12345678901234.12</v>
@@ -2926,7 +2926,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C120" t="n">
         <v>12345678901234.12</v>
@@ -2947,7 +2947,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C121" t="n">
         <v>12345678901234.12</v>
@@ -2968,7 +2968,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C122" t="n">
         <v>12345678901234.12</v>
@@ -2989,7 +2989,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C123" t="n">
         <v>12345678901234.12</v>
@@ -3010,7 +3010,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C124" t="n">
         <v>12345678901234.12</v>
@@ -3031,7 +3031,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C125" t="n">
         <v>12345678901234.12</v>
@@ -3052,7 +3052,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C126" t="n">
         <v>12345678901234.12</v>
@@ -3073,7 +3073,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C127" t="n">
         <v>12345678901234.12</v>
@@ -3094,7 +3094,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C128" t="n">
         <v>12345678901234.12</v>
@@ -3115,7 +3115,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C129" t="n">
         <v>12345678901234.12</v>
@@ -3136,7 +3136,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C130" t="n">
         <v>12345678901234.12</v>
@@ -3157,7 +3157,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>9.223372036854776e+18</v>
+        <v>9.223372036854775e+18</v>
       </c>
       <c r="C131" t="n">
         <v>12345678901234.12</v>
